--- a/artfynd/A 32067-2024 artfynd.xlsx
+++ b/artfynd/A 32067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103401893</v>
+        <v>103401896</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551999.294309628</v>
+        <v>552074</v>
       </c>
       <c r="R2" t="n">
-        <v>7017042.849170765</v>
+        <v>7016935</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103401894</v>
+        <v>103995950</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552054.8549310076</v>
+        <v>552133</v>
       </c>
       <c r="R3" t="n">
-        <v>7016979.827074305</v>
+        <v>7016922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +863,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103995924</v>
+        <v>103995956</v>
       </c>
       <c r="B4" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1841</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551973.1574728529</v>
+        <v>551973</v>
       </c>
       <c r="R4" t="n">
-        <v>7017042.426899251</v>
+        <v>7017008</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +958,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +968,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,37 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103995927</v>
+        <v>103995967</v>
       </c>
       <c r="B5" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552072.1250526845</v>
+        <v>552134</v>
       </c>
       <c r="R5" t="n">
-        <v>7016971.103518528</v>
+        <v>7016912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,15 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103995888</v>
+        <v>103401894</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552058.9325688526</v>
+        <v>552055</v>
       </c>
       <c r="R6" t="n">
-        <v>7016978.542595584</v>
+        <v>7016980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,22 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,62 +1201,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103995950</v>
+        <v>103995927</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552132.4267991525</v>
+        <v>552072</v>
       </c>
       <c r="R7" t="n">
-        <v>7016921.662725084</v>
+        <v>7016971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1287,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1297,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,6 +1326,335 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103995924</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97453</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>551973</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7017043</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103401893</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>551999</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7017043</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103995888</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552059</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7016979</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 32067-2024 artfynd.xlsx
+++ b/artfynd/A 32067-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995950</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995956</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995967</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995924</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401893</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,8 +1704,24 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995888</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>